--- a/data/trans_orig/Q5411-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2007</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7674</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8963</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52110</t>
+          <t>52126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80530</t>
+          <t>80903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6069</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>47329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58231</t>
+          <t>58530</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65801</t>
+          <t>65811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11039</t>
+          <t>10859</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>15798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60715</t>
+          <t>60895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69920</t>
+          <t>69962</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23243</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80758</t>
+          <t>80232</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91698</t>
+          <t>91943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25206</t>
+          <t>24874</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>10931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32354</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234866</t>
+          <t>235198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250358</t>
+          <t>250478</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74768</t>
+          <t>74821</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84018</t>
+          <t>83653</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313470</t>
+          <t>313573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331998</t>
+          <t>331951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,99%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46489</t>
+          <t>47061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>54476</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71557</t>
+          <t>71068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87495</t>
+          <t>86779</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122450</t>
+          <t>123057</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139850</t>
+          <t>140068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50267</t>
+          <t>50618</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26797</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51603</t>
+          <t>51404</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>374803</t>
+          <t>374452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>398877</t>
+          <t>398667</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377112</t>
+          <t>377311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>401918</t>
+          <t>403338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19377</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39287</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50678</t>
+          <t>50278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82380</t>
+          <t>82118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74645</t>
+          <t>76510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111472</t>
+          <t>115325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>462264</t>
+          <t>462610</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>482153</t>
+          <t>482174</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594462</t>
+          <t>594724</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>626164</t>
+          <t>626564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1066921</t>
+          <t>1063068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1103748</t>
+          <t>1101883</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2012</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>10781</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12892</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32836</t>
+          <t>33137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18422</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56702</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68073</t>
+          <t>68119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16613</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>48617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59515</t>
+          <t>59522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62918</t>
+          <t>62997</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76194</t>
+          <t>76322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106305</t>
+          <t>106234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115892</t>
+          <t>115817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41605</t>
+          <t>41350</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51527</t>
+          <t>52355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151647</t>
+          <t>152808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166210</t>
+          <t>166673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>24207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48442</t>
+          <t>48083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35918</t>
+          <t>35722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>63237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183311</t>
+          <t>183670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208082</t>
+          <t>207546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40179</t>
+          <t>40230</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53134</t>
+          <t>53350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>229926</t>
+          <t>228611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>255930</t>
+          <t>256126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20912</t>
+          <t>20955</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41893</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67194</t>
+          <t>67630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>52917</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82161</t>
+          <t>82471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81784</t>
+          <t>81741</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96153</t>
+          <t>95328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>121206</t>
+          <t>120770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146507</t>
+          <t>146719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208935</t>
+          <t>208625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>238179</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66846</t>
+          <t>66648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101475</t>
+          <t>100047</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>65851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99480</t>
+          <t>99670</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>293229</t>
+          <t>294657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>327858</t>
+          <t>328056</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>297212</t>
+          <t>297022</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>330175</t>
+          <t>330841</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,4%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46769</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>80660</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138941</t>
+          <t>142271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>186050</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>199506</t>
+          <t>198236</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255609</t>
+          <t>255460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>478977</t>
+          <t>482159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>512868</t>
+          <t>514686</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>555955</t>
+          <t>553664</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>603064</t>
+          <t>599734</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1046033</t>
+          <t>1046182</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1102136</t>
+          <t>1103406</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2016</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60192</t>
+          <t>58681</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93111</t>
+          <t>94092</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104142</t>
+          <t>104157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44681</t>
+          <t>44455</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52375</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>59639</t>
+          <t>60384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69020</t>
+          <t>69087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20409</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106018</t>
+          <t>105928</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116635</t>
+          <t>116546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>34857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44943</t>
+          <t>44955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146061</t>
+          <t>145927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159444</t>
+          <t>159556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>26444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19608</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19507</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>39813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177027</t>
+          <t>177412</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192016</t>
+          <t>192285</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79438</t>
+          <t>79876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>93644</t>
+          <t>94300</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262064</t>
+          <t>263089</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>283395</t>
+          <t>283209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>8847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>11966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30017</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48682</t>
+          <t>48893</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121404</t>
+          <t>121827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135684</t>
+          <t>136374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129533</t>
+          <t>129178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147325</t>
+          <t>147584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>256089</t>
+          <t>255878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279842</t>
+          <t>278962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46774</t>
+          <t>46578</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>80403</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46774</t>
+          <t>46578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80865</t>
+          <t>80403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332218</t>
+          <t>332680</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>366309</t>
+          <t>366505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>332218</t>
+          <t>332680</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366309</t>
+          <t>366505</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37005</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60470</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83987</t>
+          <t>82408</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126777</t>
+          <t>126671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129382</t>
+          <t>127374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177621</t>
+          <t>175911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>530858</t>
+          <t>530466</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>554323</t>
+          <t>555447</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>645587</t>
+          <t>645693</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>688377</t>
+          <t>689956</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1186071</t>
+          <t>1187781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1234310</t>
+          <t>1236318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de usar el baño o ducha en 2023</t>
+          <t>Población según si es capaz de usar el baño o ducha en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9817</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102263</t>
+          <t>102633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106998</t>
+          <t>106977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57303</t>
+          <t>56896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64848</t>
+          <t>64921</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163083</t>
+          <t>161878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>171047</t>
+          <t>170972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9927</t>
+          <t>10816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>14710</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85071</t>
+          <t>84182</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93207</t>
+          <t>93089</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>38998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45484</t>
+          <t>45007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127668</t>
+          <t>127219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>137318</t>
+          <t>136976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>13293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>88776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97543</t>
+          <t>97775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43899</t>
+          <t>43608</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49799</t>
+          <t>49932</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135572</t>
+          <t>135966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>145954</t>
+          <t>146037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18481</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34112</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>2080</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>30439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13321</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60924</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204085</t>
+          <t>203686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219716</t>
+          <t>220205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295394</t>
+          <t>296254</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324907</t>
+          <t>324613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>503966</t>
+          <t>505033</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>551569</t>
+          <t>550553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>29351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43307</t>
+          <t>44017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>36338</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53709</t>
+          <t>53148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78399</t>
+          <t>78053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86983</t>
+          <t>86991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161475</t>
+          <t>160765</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176251</t>
+          <t>175431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243079</t>
+          <t>243640</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260378</t>
+          <t>260450</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,76%</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>51348</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70797</t>
+          <t>70870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51753</t>
+          <t>51820</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71627</t>
+          <t>71981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250275</t>
+          <t>250202</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270169</t>
+          <t>269724</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>252649</t>
+          <t>252295</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>272523</t>
+          <t>272456</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60510</t>
+          <t>60360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58940</t>
+          <t>60821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>154048</t>
+          <t>152989</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105308</t>
+          <t>107075</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198173</t>
+          <t>197988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577543</t>
+          <t>577693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599865</t>
+          <t>599482</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>863540</t>
+          <t>864599</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>958648</t>
+          <t>956767</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1457467</t>
+          <t>1457652</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1550332</t>
+          <t>1548565</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5411-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5411-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52126</t>
+          <t>52063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80903</t>
+          <t>81258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5887</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47329</t>
+          <t>46212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>58530</t>
+          <t>59093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65811</t>
+          <t>65812</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15798</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60895</t>
+          <t>60970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69962</t>
+          <t>69884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80232</t>
+          <t>80625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91943</t>
+          <t>92046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24874</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10931</t>
+          <t>11481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13873</t>
+          <t>13787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>31269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235198</t>
+          <t>235363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250478</t>
+          <t>250198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74821</t>
+          <t>74271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83653</t>
+          <t>83751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>313573</t>
+          <t>314555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331951</t>
+          <t>332037</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25182</t>
+          <t>25104</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>11726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28658</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47061</t>
+          <t>47273</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54476</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71068</t>
+          <t>71146</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86779</t>
+          <t>86838</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>122244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140068</t>
+          <t>139989</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26403</t>
+          <t>25707</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>51160</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51404</t>
+          <t>52250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>374452</t>
+          <t>373910</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>398667</t>
+          <t>399363</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377311</t>
+          <t>376465</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>403338</t>
+          <t>401123</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19377</t>
+          <t>20111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50278</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76510</t>
+          <t>74454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115325</t>
+          <t>110855</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>462610</t>
+          <t>462296</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>482174</t>
+          <t>481440</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>594724</t>
+          <t>594513</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>626564</t>
+          <t>627369</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1063068</t>
+          <t>1067538</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1101883</t>
+          <t>1103939</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6777</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33137</t>
+          <t>32951</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56315</t>
+          <t>55793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68119</t>
+          <t>68084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12013</t>
+          <t>13391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16534</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48617</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59522</t>
+          <t>59518</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62997</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>76314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>12332</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>12049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>21090</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>106234</t>
+          <t>106321</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115817</t>
+          <t>115931</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41350</t>
+          <t>42566</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52355</t>
+          <t>52371</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152808</t>
+          <t>152178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166673</t>
+          <t>166297</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24207</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>47906</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35722</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63237</t>
+          <t>62417</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183670</t>
+          <t>183847</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207546</t>
+          <t>207491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>40393</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53350</t>
+          <t>52948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228611</t>
+          <t>229431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256126</t>
+          <t>256718</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7368</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20955</t>
+          <t>21176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41681</t>
+          <t>42233</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67630</t>
+          <t>68280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52917</t>
+          <t>52959</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82471</t>
+          <t>81668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81741</t>
+          <t>81520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95328</t>
+          <t>95362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120770</t>
+          <t>120120</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146719</t>
+          <t>146167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208625</t>
+          <t>209428</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238179</t>
+          <t>238137</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66648</t>
+          <t>66779</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100047</t>
+          <t>99766</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65851</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99670</t>
+          <t>100246</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>294657</t>
+          <t>294938</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>328056</t>
+          <t>327925</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>297022</t>
+          <t>296446</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>330841</t>
+          <t>330166</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44951</t>
+          <t>46468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>78774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>142271</t>
+          <t>138834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>188341</t>
+          <t>185655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>198236</t>
+          <t>196688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255460</t>
+          <t>253426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>482159</t>
+          <t>480863</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>514686</t>
+          <t>513169</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>553664</t>
+          <t>556350</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>599734</t>
+          <t>603171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1046182</t>
+          <t>1048216</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1103406</t>
+          <t>1104954</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58681</t>
+          <t>59749</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28804</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94092</t>
+          <t>93676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104157</t>
+          <t>104173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44455</t>
+          <t>44680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>52312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60384</t>
+          <t>59848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69087</t>
+          <t>69099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>15569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105928</t>
+          <t>104692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>116546</t>
+          <t>116129</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34857</t>
+          <t>35284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44955</t>
+          <t>44923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145927</t>
+          <t>145002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159556</t>
+          <t>159136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>40119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177412</t>
+          <t>176265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192285</t>
+          <t>191872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79876</t>
+          <t>79654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94300</t>
+          <t>93894</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263089</t>
+          <t>262783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>283209</t>
+          <t>284375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23394</t>
+          <t>23821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30372</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25809</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48893</t>
+          <t>48169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121827</t>
+          <t>121400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136374</t>
+          <t>135871</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129178</t>
+          <t>129516</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147584</t>
+          <t>148164</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>255878</t>
+          <t>256602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>278962</t>
+          <t>279905</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46578</t>
+          <t>46949</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80403</t>
+          <t>81272</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46578</t>
+          <t>46949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>80403</t>
+          <t>81272</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332680</t>
+          <t>331811</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>366505</t>
+          <t>366134</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>332680</t>
+          <t>331811</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366505</t>
+          <t>366134</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60862</t>
+          <t>60684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82408</t>
+          <t>80998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126671</t>
+          <t>124930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127374</t>
+          <t>126322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>175911</t>
+          <t>176431</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>530466</t>
+          <t>530644</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>555447</t>
+          <t>554457</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>645693</t>
+          <t>647434</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>689956</t>
+          <t>691366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1187781</t>
+          <t>1187261</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1236318</t>
+          <t>1237370</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2648</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>513</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8425</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11022</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>105513</t>
+          <t>118263</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102633</t>
+          <t>115212</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106977</t>
+          <t>119865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>62883</t>
+          <t>71911</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56896</t>
+          <t>63527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64921</t>
+          <t>74046</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>168396</t>
+          <t>190173</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>161878</t>
+          <t>182498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170972</t>
+          <t>193088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10816</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>15155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>90486</t>
+          <t>99930</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>84182</t>
+          <t>94806</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93089</t>
+          <t>102888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>51536</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38998</t>
+          <t>47713</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>53649</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>133597</t>
+          <t>151466</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127219</t>
+          <t>144945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136976</t>
+          <t>155189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13293</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9181</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>14243</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94228</t>
+          <t>104217</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88776</t>
+          <t>98993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97775</t>
+          <t>107835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47389</t>
+          <t>51981</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43608</t>
+          <t>48113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49932</t>
+          <t>54869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141618</t>
+          <t>156198</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>149697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>146037</t>
+          <t>161077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25369</t>
+          <t>27223</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>19342</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>36765</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>11434</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>35690</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59857</t>
+          <t>49338</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>212828</t>
+          <t>232783</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203686</t>
+          <t>223241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>220205</t>
+          <t>240664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>316372</t>
+          <t>119446</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296254</t>
+          <t>114536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324613</t>
+          <t>123524</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>529200</t>
+          <t>352229</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>505033</t>
+          <t>341548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>550553</t>
+          <t>361830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8792</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>35695</t>
+          <t>38413</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>30349</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>47331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>47204</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53148</t>
+          <t>57012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83423</t>
+          <t>92001</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78053</t>
+          <t>86158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86991</t>
+          <t>95728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>169087</t>
+          <t>181453</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160765</t>
+          <t>172535</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175431</t>
+          <t>189517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>252511</t>
+          <t>273456</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>243640</t>
+          <t>263648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>260450</t>
+          <t>282742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,18%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>518</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,67 +10383,67 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>60838</t>
+          <t>65514</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51348</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70870</t>
+          <t>76404</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
+          <t>18,98%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>22,14%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>66032</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>56624</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>77752</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>18,95%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>61328</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>51820</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>71981</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>18,91%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,32%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,67 +10496,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>260234</t>
+          <t>279622</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250202</t>
+          <t>268732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>269724</t>
+          <t>290611</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
+          <t>81,02%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>77,86%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>282380</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>270660</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>291788</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
           <t>81,05%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>77,93%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>262948</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>252295</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>272456</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>81,09%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>321072</t>
+          <t>345136</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>321072</t>
+          <t>345136</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>321072</t>
+          <t>345136</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>324276</t>
+          <t>348412</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>324276</t>
+          <t>348412</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>324276</t>
+          <t>348412</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>48861</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>40356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60360</t>
+          <t>63698</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>118511</t>
+          <t>127847</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60821</t>
+          <t>113384</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>152989</t>
+          <t>143557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>167372</t>
+          <t>179557</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>107075</t>
+          <t>160688</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>197988</t>
+          <t>199729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>589192</t>
+          <t>649953</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>577693</t>
+          <t>637965</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>599482</t>
+          <t>661307</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>899077</t>
+          <t>755949</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>864599</t>
+          <t>740239</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>956767</t>
+          <t>770412</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1488268</t>
+          <t>1405902</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1457652</t>
+          <t>1385730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1548565</t>
+          <t>1424771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1017588</t>
+          <t>883796</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1017588</t>
+          <t>883796</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1017588</t>
+          <t>883796</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1655640</t>
+          <t>1585459</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1655640</t>
+          <t>1585459</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1655640</t>
+          <t>1585459</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
